--- a/Frontend-Interview.xlsx
+++ b/Frontend-Interview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="581">
   <si>
     <t>Group</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Rendering and Basic Display</t>
   </si>
   <si>
-    <t>Junior</t>
+    <t>junior</t>
   </si>
   <si>
     <t>Yes. See Figma sheet</t>
@@ -49,7 +49,7 @@
     <t>Sorting and Filtering</t>
   </si>
   <si>
-    <t>Junior to Mid</t>
+    <t>mid</t>
   </si>
   <si>
     <t>Debounce vs throttle, race conditions, composed predicates, filter persistence via URL, multi-column sort, saved search</t>
@@ -58,9 +58,6 @@
     <t>Pagination</t>
   </si>
   <si>
-    <t>Mid</t>
-  </si>
-  <si>
     <t>Offset vs cursor pagination, IntersectionObserver, virtual scroll, page size side effects, prefetch, unknown total count</t>
   </si>
   <si>
@@ -73,9 +70,6 @@
     <t>Performance</t>
   </si>
   <si>
-    <t>Mid to Senior</t>
-  </si>
-  <si>
     <t>Core Web Vitals, trackBy, OnPush immutability, Web Workers, requestAnimationFrame, code splitting, lazy image loading</t>
   </si>
   <si>
@@ -94,7 +88,7 @@
     <t>Micro-Frontend</t>
   </si>
   <si>
-    <t>Senior</t>
+    <t>senior</t>
   </si>
   <si>
     <t>Singleton shared libs, URL params communication, CustomEvent bus, Remote error boundary, contract testing, bundle deduplication</t>
@@ -142,7 +136,10 @@
     <t>Red Flags to Watch For</t>
   </si>
   <si>
-    <t>junior</t>
+    <t>Figma Link</t>
+  </si>
+  <si>
+    <t>Why This Question?</t>
   </si>
   <si>
     <t>You need to display 100 records from an API in a table. Where do you put the data-fetching logic, inside the component or somewhere else, and why?</t>
@@ -154,6 +151,9 @@
     <t>Says "just put it in the component, it is simpler". Cannot explain why separation matters for maintainability.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-16991&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
     <t>The API takes 3 seconds to respond. What should the user see during that wait, and how do you implement it?</t>
   </si>
   <si>
@@ -163,6 +163,9 @@
     <t>Only mentions a spinner without considering error or empty states. Does not think about perceived performance.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-17635&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
     <t>The API returns an empty array. Should you show nothing, "No data found", or a designed empty state? How do you decide?</t>
   </si>
   <si>
@@ -172,6 +175,9 @@
     <t>Says "just hide the table". Does not distinguish filter-empty from truly-empty scenarios.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-18027&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
     <t>A date column shows "2024-01-05T10:30:00Z" from the API. Where and how do you format it for display?</t>
   </si>
   <si>
@@ -181,6 +187,15 @@
     <t>Formats directly in the template with string operations. Does not think about locale or timezone differences.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-20754&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This question tests whether the candidate treats "formatting a date" as a trivial string problem or recognizes it touches timezone conversion, locale/i18n, and where in the app raw vs. display data should live.
+Junior: formats inline with hardcoded strings, ignores timezone, repeats logic per component.
+Senior: keeps raw ISO data in state, converts to local time only at display time (Intl.DateTimeFormat or a lib), uses a shared formatting util, and considers locale + edge cases (invalid dates, relative vs absolute time).
+Date/timezone bugs are a very common real-world source of production issues, so this is a good low-effort way to surface architecture thinking.</t>
+  </si>
+  <si>
     <t>Your table has 8 columns but on a mobile screen only 3 can fit. How do you approach this?</t>
   </si>
   <si>
@@ -190,6 +205,14 @@
     <t>Says "just scroll horizontally" without any discussion of column priority or user experience trade-offs.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-22746&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This tests responsive UX thinking, not CSS tricks.
+Junior: shrinks fonts/padding to cram everything in, or just adds horizontal scroll.
+Senior: picks which columns matter most on mobile, then uses a real pattern, expandable rows, card/list layout, or a column picker, and asks "which data does the user actually need here?" before designing.</t>
+  </si>
+  <si>
     <t>A row has a "Delete" button. The user clicks it. Walk me through what should happen before, during, and after the delete.</t>
   </si>
   <si>
@@ -199,6 +222,12 @@
     <t>Deletes immediately without confirmation. Does not handle loading or error states. Does not think about focus management.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-24489&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t>This statement reveals your level right away. Juniors think about the happy path, mid-level engineers think about error states, and seniors think about focus management and rollback.</t>
+  </si>
+  <si>
     <t>How would you implement a "Status" column that shows colored badges like green for Active, red for Inactive, and grey for Draft?</t>
   </si>
   <si>
@@ -208,6 +237,15 @@
     <t>Uses inline styles with hardcoded hex colors. Duplicates badge logic in every table that needs it.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=8-25576&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This question separates junior from senior not by whether the code runs, but by how they structure it for change.
+Junior: hardcodes if/else per status, repeats styles inline, no fallback for unknown values, no thought for accessibility.
+Senior: uses a status → style lookup/config (easy to extend), adds a default fallback, builds a reusable Badge component, and often asks clarifying questions like "where does this status come from, a fixed enum or dynamic backend data?"
+So the real signal is maintainability thinking, how they'd handle a new status being added later, not just getting today's version working.</t>
+  </si>
+  <si>
     <t>What is the difference between "rendering" and "painting" in the browser? Why should a frontend developer care about this distinction?</t>
   </si>
   <si>
@@ -235,6 +273,15 @@
     <t>Accepts that all 10 re-render as normal behavior. Does not know about memoization or granular reactivity.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=8-33923&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root problem: Angular's default Change Detection runs through the entire component tree on any event, not just where data changed.
+Junior: doesn't know OnPush, or uses it but still mutates data directly, so CD still misses the change.
+Senior: applies OnPush + immutable updates (new object/array refs) + trackBy in *ngFor (or Signals in newer Angular) so only the actually-changed component re-checks.
+Signal: does the candidate understand why full-tree CD happens (senior), or just call OnPush/markForCheck() as a magic fix (junior)?</t>
+  </si>
+  <si>
     <t>What is the difference between server-side rendering, client-side rendering, and static site generation? When would you choose each for a data table?</t>
   </si>
   <si>
@@ -289,9 +336,6 @@
     <t>Only knows controlled components. Cannot explain why uncontrolled components exist or when they are appropriate.</t>
   </si>
   <si>
-    <t>mid</t>
-  </si>
-  <si>
     <t>User clicks a column header to sort. Should you sort client-side or server-side? What factors influence this decision?</t>
   </si>
   <si>
@@ -427,6 +471,9 @@
     <t>Accepts the flickering result as an API timing issue with no fix. Does not understand request cancellation.</t>
   </si>
   <si>
+    <t>Don't ask about theory, ask about symptoms. Strong candidates recognize a race condition immediately, while weaker candidates blame the API</t>
+  </si>
+  <si>
     <t>What is the difference between offset-based and cursor-based pagination? When would you choose each?</t>
   </si>
   <si>
@@ -526,6 +573,12 @@
     <t>Does not recognize this as a known problem of offset pagination. Has no solution or mitigation strategy.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=22-3499&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t>No one thinks about this until it causes a bug in production. Candidates who know the answer have usually built or debugged real-world pagination, not just used a library. Offset pagination silently corrupts data under concurrent mutations because your dev environment never has two users modifying the same dataset at the same time.</t>
+  </si>
+  <si>
     <t>How do you make pagination accessible to keyboard and screen reader users?</t>
   </si>
   <si>
@@ -553,6 +606,12 @@
     <t>Tries to fetch all 10,000 records to collect their IDs. This is a terrible UX and performance decision.</t>
   </si>
   <si>
+    <t>https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=22-3428&amp;t=hXp9MqWKOyeJVdxi-0</t>
+  </si>
+  <si>
+    <t>This question separates engineers who have actually built the feature from those who have only used a UI library. Someone who truly understands it should be able to explain the isAllSelected flag and the deselected Set.</t>
+  </si>
+  <si>
     <t>User selects 50 rows and clicks "Delete." The API processes them one at a time. How do you show progress and handle partial failures?</t>
   </si>
   <si>
@@ -697,6 +756,9 @@
     <t>Cannot explain why mutation fails with OnPush. Suggests calling detectChanges manually everywhere, which defeats the purpose of OnPush.</t>
   </si>
   <si>
+    <t>This is a very strong differentiator between people who understand reactivity and those who just copy-paste code. Without understanding immutability, they won't be able to answer this question no matter how much documentation they've read.</t>
+  </si>
+  <si>
     <t>What are Core Web Vitals and which ones are most directly affected by a heavy data table?</t>
   </si>
   <si>
@@ -796,6 +858,9 @@
     <t>Cannot describe the snapshot step. Shows an error but does not restore the deleted row to the UI.</t>
   </si>
   <si>
+    <t>It's very specific. Candidates should know to take a snapshot before the mutation, restore the UI if it fails, re-enable the button, and display an error message. Those who haven't implemented it before usually can't walk through all the steps.</t>
+  </si>
+  <si>
     <t>Compare polling versus WebSocket for real-time table updates. What factors guide your choice?</t>
   </si>
   <si>
@@ -949,6 +1014,9 @@
     <t>Does not recognize the race condition with concurrent requests. Uses a single isLoading boolean for all requests on the page.</t>
   </si>
   <si>
+    <t>It's a simple question, but it separates engineers who've actually debugged production issues from those who've only followed tutorials.</t>
+  </si>
+  <si>
     <t>Describe the observer or reactive pattern. How does it relate to how your table subscribes to data updates?</t>
   </si>
   <si>
@@ -985,9 +1053,6 @@
     <t>The table directly holds a reference to the details panel component and calls methods on it. This creates tight coupling that prevents independent testing.</t>
   </si>
   <si>
-    <t>senior</t>
-  </si>
-  <si>
     <t>Your table component is in a Remote app. The Shell lazily loads it. What must be configured for Angular DI to work without duplicate instances?</t>
   </si>
   <si>
@@ -1024,6 +1089,9 @@
     <t>Assumes teams will coordinate manually via chat. Does not know about contract testing.</t>
   </si>
   <si>
+    <t>This question tests whether the candidate has a distributed ownership mindset, something junior and mid-level engineers often don't think about because they haven't worked in larger teams yet.</t>
+  </si>
+  <si>
     <t>The Remote deployment fails halfway. Shell users get a blank table. How do you handle this at the Shell level?</t>
   </si>
   <si>
@@ -1123,6 +1191,9 @@
     <t>Accepts focus loss as normal behavior. Has never considered focus management for dynamic DOM changes.</t>
   </si>
   <si>
+    <t>Most frontend developers don't consider focus management. Candidates who understand this are usually the ones who have worked with real accessibility requirements, rather than just knowing the theory.</t>
+  </si>
+  <si>
     <t>Your table has 50 rows each with a "View Details" link. All 50 links say "View Details." Why is this an accessibility problem?</t>
   </si>
   <si>
@@ -1312,6 +1383,9 @@
     <t>Has never heard of CSV injection. Thinks CSV files are inherently safe because they contain no HTML or JavaScript.</t>
   </si>
   <si>
+    <t>Most frontend candidates don't even know that CSV injection exists. This question isn't meant to test whether they already know it, it tests how they respond when given a hint, which says a lot about their security mindset.</t>
+  </si>
+  <si>
     <t>A search input sends user-typed text to the API. What injection risks exist on the frontend side?</t>
   </si>
   <si>
@@ -1693,7 +1767,7 @@
     <t>Recommended if you have no Figma design experience. Screenshot a table from any admin UI (e.g. GitHub issues list) and paste it. Add sticky notes per question group.</t>
   </si>
   <si>
-    <t>{"stars":[],"highlights":["g1_q0","g1_q1","g1_q2"],"customs":{"1":[]}}</t>
+    <t>{"stars":[],"highlights":["g1_q5","g2_q14","g4_q1","g6_q3","g7_q7","g11_q1","g3_q10","g5_q5","g8_q3","g9_q2","g1_q6","g1_q3","g1_q4","g1_q9"],"customs":{},"figmaLinks":{"g1_q5":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-24489&amp;t=hXp9MqWKOyeJVdxi-0","g1_q6":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=8-25576&amp;t=hXp9MqWKOyeJVdxi-0","g1_q3":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-20754&amp;t=hXp9MqWKOyeJVdxi-0","g1_q4":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=2-22746&amp;t=hXp9MqWKOyeJVdxi-0","g1_q0":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-16991&amp;t=hXp9MqWKOyeJVdxi-0","g1_q1":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-17635&amp;t=hXp9MqWKOyeJVdxi-0","g1_q2":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=1-18027&amp;t=hXp9MqWKOyeJVdxi-0","g1_q9":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=8-33923&amp;t=hXp9MqWKOyeJVdxi-0","g3_q10":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=22-3499&amp;t=hXp9MqWKOyeJVdxi-0","g4_q1":"https://www.figma.com/design/cmDAWJpOVFBtVE4NiEbvKy/150-questions?node-id=22-3428&amp;t=hXp9MqWKOyeJVdxi-0"},"qEdits":{"g1_q5":{"w":"This statement reveals your level right away. Juniors think about the happy path, mid-level engineers think about error states, and seniors think about focus management and rollback."},"g2_q14":{"w":"Don't ask about theory, ask about symptoms. Strong candidates recognize a race condition immediately, while weaker candidates blame the API"},"g4_q1":{"w":"This question separates engineers who have actually built the feature from those who have only used a UI library. Someone who truly understands it should be able to explain the isAllSelected flag and the deselected Set."},"g6_q3":{"w":"It's very specific. Candidates should know to take a snapshot before the mutation, restore the UI if it fails, re-enable the button, and display an error message. Those who haven't implemented it before usually can't walk through all the steps."},"g7_q7":{"w":"It's a simple question, but it separates engineers who've actually debugged production issues from those who've only followed tutorials."},"g11_q1":{"w":"Most frontend candidates don't even know that CSV injection exists. This question isn't meant to test whether they already know it, it tests how they respond when given a hint, which says a lot about their security mindset."},"g3_q10":{"w":"No one thinks about this until it causes a bug in production. Candidates who know the answer have usually built or debugged real-world pagination, not just used a library. Offset pagination silently corrupts data under concurrent mutations because your dev environment never has two users modifying the same dataset at the same time."},"g5_q5":{"w":"This is a very strong differentiator between people who understand reactivity and those who just copy-paste code. Without understanding immutability, they won't be able to answer this question no matter how much documentation they've read."},"g8_q3":{"w":"This question tests whether the candidate has a distributed ownership mindset, something junior and mid-level engineers often don't think about because they haven't worked in larger teams yet."},"g9_q2":{"w":"Most frontend developers don't consider focus management. Candidates who understand this are usually the ones who have worked with real accessibility requirements, rather than just knowing the theory."},"g1_q6":{"w":"This question separates junior from senior not by whether the code runs, but by how they structure it for change.\nJunior: hardcodes if/else per status, repeats styles inline, no fallback for unknown values, no thought for accessibility.\nSenior: uses a status → style lookup/config (easy to extend), adds a default fallback, builds a reusable Badge component, and often asks clarifying questions like \"where does this status come from, a fixed enum or dynamic backend data?\"\nSo the real signal is maintainability thinking, how they'd handle a new status being added later, not just getting today's version working."},"g1_q3":{"w":"This question tests whether the candidate treats \"formatting a date\" as a trivial string problem or recognizes it touches timezone conversion, locale/i18n, and where in the app raw vs. display data should live.\nJunior: formats inline with hardcoded strings, ignores timezone, repeats logic per component.\nSenior: keeps raw ISO data in state, converts to local time only at display time (Intl.DateTimeFormat or a lib), uses a shared formatting util, and considers locale + edge cases (invalid dates, relative vs absolute time).\nDate/timezone bugs are a very common real-world source of production issues, so this is a good low-effort way to surface architecture thinking."},"g1_q4":{"w":"This tests responsive UX thinking, not CSS tricks.\nJunior: shrinks fonts/padding to cram everything in, or just adds horizontal scroll.\nSenior: picks which columns matter most on mobile, then uses a real pattern, expandable rows, card/list layout, or a column picker, and asks \"which data does the user actually need here?\" before designing."},"g1_q9":{"w":"Root problem: Angular's default Change Detection runs through the entire component tree on any event, not just where data changed.\nJunior: doesn't know OnPush, or uses it but still mutates data directly, so CD still misses the change.\nSenior: applies OnPush + immutable updates (new object/array refs) + trackBy in *ngFor (or Signals in newer Angular) so only the actually-changed component re-checks.\nSignal: does the candidate understand why full-tree CD happens (senior), or just call OnPush/markForCheck() as a magic fix (junior)?"}}}</t>
   </si>
 </sst>
 </file>
@@ -1764,13 +1838,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2192,7 +2269,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2">
         <v>12</v>
@@ -2201,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2209,10 +2286,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2">
         <v>12</v>
@@ -2221,7 +2298,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2229,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2">
         <v>13</v>
@@ -2241,7 +2318,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2249,10 +2326,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2">
         <v>13</v>
@@ -2261,7 +2338,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2269,10 +2346,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2">
         <v>12</v>
@@ -2281,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2289,10 +2366,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2">
         <v>12</v>
@@ -2301,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2309,10 +2386,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D10" s="2">
         <v>12</v>
@@ -2321,7 +2398,7 @@
         <v>8</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2329,10 +2406,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2">
         <v>10</v>
@@ -2341,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2349,10 +2426,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2">
         <v>11</v>
@@ -2361,7 +2438,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2369,10 +2446,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>12</v>
@@ -2381,27 +2458,27 @@
         <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2412,7 +2489,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2423,7 +2500,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2431,159 +2508,207 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="H2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="G3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="F4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="E5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -2591,19 +2716,25 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -2611,39 +2742,51 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+        <v>79</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>1</v>
       </c>
@@ -2651,19 +2794,25 @@
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>1</v>
       </c>
@@ -2671,19 +2820,25 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>1</v>
       </c>
@@ -2691,19 +2846,25 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>1</v>
       </c>
@@ -2711,19 +2872,25 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>1</v>
       </c>
@@ -2731,19 +2898,25 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>1</v>
       </c>
@@ -2751,19 +2924,25 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2</v>
       </c>
@@ -2771,19 +2950,25 @@
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2</v>
       </c>
@@ -2791,19 +2976,25 @@
         <v>10</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2</v>
       </c>
@@ -2811,19 +3002,25 @@
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2</v>
       </c>
@@ -2831,19 +3028,25 @@
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2</v>
       </c>
@@ -2851,19 +3054,25 @@
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2</v>
       </c>
@@ -2871,19 +3080,25 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2</v>
       </c>
@@ -2891,19 +3106,25 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2</v>
       </c>
@@ -2911,19 +3132,25 @@
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2</v>
       </c>
@@ -2931,19 +3158,25 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2</v>
       </c>
@@ -2951,19 +3184,25 @@
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2</v>
       </c>
@@ -2971,19 +3210,25 @@
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2</v>
       </c>
@@ -2991,19 +3236,25 @@
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="30" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2</v>
       </c>
@@ -3011,19 +3262,25 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2</v>
       </c>
@@ -3031,39 +3288,51 @@
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+        <v>144</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>2</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>3</v>
       </c>
@@ -3071,19 +3340,25 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>3</v>
       </c>
@@ -3091,19 +3366,25 @@
         <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -3111,19 +3392,25 @@
         <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>3</v>
       </c>
@@ -3131,19 +3418,25 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>3</v>
       </c>
@@ -3151,19 +3444,25 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>3</v>
       </c>
@@ -3171,19 +3470,25 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="39" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>3</v>
       </c>
@@ -3191,19 +3496,25 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="40" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>3</v>
       </c>
@@ -3211,19 +3522,25 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="41" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>3</v>
       </c>
@@ -3231,19 +3548,25 @@
         <v>13</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="42" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -3251,39 +3574,51 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="43" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+        <v>178</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
         <v>3</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>3</v>
       </c>
@@ -3291,2156 +3626,2804 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>4</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="46" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+        <v>189</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
         <v>4</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="47" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>4</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="48" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>4</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="49" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>4</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="50" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>4</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>4</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="52" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>4</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="53" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>4</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>4</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="55" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>4</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="56" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>4</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>5</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>5</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>5</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>5</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>5</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="62" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+        <v>239</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
         <v>5</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="63" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>5</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="64" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>5</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="65" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>5</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="66" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>5</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="67" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>5</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="68" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>5</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>5</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="70" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="71" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="71" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="72" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="73" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+        <v>273</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
         <v>6</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="74" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B73" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="74" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="75" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>6</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="76" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="76" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="77" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>6</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="78" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="79" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="80" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>6</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="81" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="81" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="82" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="82" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>6</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="83" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>7</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="84" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>7</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="85" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="85" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>7</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="86" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="86" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>7</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="87" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>7</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="88" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>7</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="89" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>7</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="90" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+        <v>325</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
         <v>7</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="91" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="91" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>7</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="92" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>7</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="93" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="93" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>7</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="94" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="94" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>7</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="95" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="95" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="96" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="96" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="97" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="97" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="98" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+        <v>350</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
         <v>8</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="99" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="99" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="100" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="101" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="102" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="103" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="104" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="104" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="105" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="105" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="106" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="106" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="107" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>9</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="108" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="108" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>9</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="109" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+        <v>384</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="109" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
         <v>9</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="110" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="110" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>9</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="111" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="111" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>9</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="112" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>9</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="113" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="113" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>9</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="114" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="114" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>9</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="115" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="115" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>9</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="116" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="116" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>9</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="117" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>9</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="118" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="118" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>9</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="119" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="119" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>10</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="120" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="120" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>10</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="121" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="121" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>10</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="122" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="122" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>10</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="123" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>10</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="124" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="124" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>10</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="125" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="125" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>10</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="126" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>10</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="127" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="127" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>10</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="128" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="128" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>10</v>
       </c>
       <c r="B128" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="129" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>11</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="129" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>11</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="130" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>11</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="131" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="130" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="4">
+        <v>11</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="131" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>11</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="132" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="132" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>11</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="133" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>11</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="134" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>11</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="135" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>11</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="136" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>11</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="137" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>11</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="138" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>11</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="139" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>11</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="140" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>12</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="141" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>12</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="142" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>12</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="143" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="143" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>12</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="144" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="144" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>12</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="145" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="145" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>12</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="146" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="146" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>12</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="147" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="147" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>12</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="148" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="148" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>12</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="149" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="149" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>12</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="150" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="150" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>12</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="151" ht="80" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="151" ht="80" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>12</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>323</v>
+        <v>24</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>494</v>
+        <v>515</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5462,223 +6445,223 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" ht="80" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +6677,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
